--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N159_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N159_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.18532954984173</v>
+        <v>5.067616051849281</v>
       </c>
       <c r="D2" t="n">
-        <v>23.75977604729774</v>
+        <v>3.860963607685883</v>
       </c>
       <c r="E2" t="n">
-        <v>7.799163418033405</v>
+        <v>1.267364055430428</v>
       </c>
       <c r="F2" t="n">
-        <v>7.264191559006734</v>
+        <v>1.180431128338594</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.15898951631297</v>
+        <v>1.813335796400857</v>
       </c>
       <c r="D3" t="n">
-        <v>15.96656455440761</v>
+        <v>2.594566740091238</v>
       </c>
       <c r="E3" t="n">
-        <v>7.799163418033405</v>
+        <v>1.267364055430428</v>
       </c>
       <c r="F3" t="n">
-        <v>7.264191559006734</v>
+        <v>1.180431128338594</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.89432939834254</v>
+        <v>3.070328527230663</v>
       </c>
       <c r="D4" t="n">
-        <v>11.89443859760054</v>
+        <v>1.932846272110088</v>
       </c>
       <c r="E4" t="n">
-        <v>7.799163418033405</v>
+        <v>1.267364055430428</v>
       </c>
       <c r="F4" t="n">
-        <v>7.264191559006734</v>
+        <v>1.180431128338594</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.00387810332661</v>
+        <v>3.088130191790575</v>
       </c>
       <c r="D5" t="n">
-        <v>18.59622315356291</v>
+        <v>3.021886262453973</v>
       </c>
       <c r="E5" t="n">
-        <v>7.799163418033405</v>
+        <v>1.267364055430428</v>
       </c>
       <c r="F5" t="n">
-        <v>7.264191559006734</v>
+        <v>1.180431128338594</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.78901674712684</v>
+        <v>3.215715221408111</v>
       </c>
       <c r="D6" t="n">
-        <v>20.24359654132074</v>
+        <v>3.289584437964621</v>
       </c>
       <c r="E6" t="n">
-        <v>7.799163418033405</v>
+        <v>1.267364055430428</v>
       </c>
       <c r="F6" t="n">
-        <v>7.264191559006734</v>
+        <v>1.180431128338594</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.52826923548729</v>
+        <v>5.610843750766685</v>
       </c>
       <c r="D7" t="n">
-        <v>35.54599645253293</v>
+        <v>5.7762244235366</v>
       </c>
       <c r="E7" t="n">
-        <v>7.799163418033405</v>
+        <v>1.267364055430428</v>
       </c>
       <c r="F7" t="n">
-        <v>7.264191559006734</v>
+        <v>1.180431128338594</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.89433379095573</v>
+        <v>5.020329241030307</v>
       </c>
       <c r="D8" t="n">
-        <v>31.24050148846187</v>
+        <v>5.076581491875054</v>
       </c>
       <c r="E8" t="n">
-        <v>7.799163418033405</v>
+        <v>1.267364055430428</v>
       </c>
       <c r="F8" t="n">
-        <v>7.264191559006734</v>
+        <v>1.180431128338594</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.90027520115163</v>
+        <v>4.69629472018714</v>
       </c>
       <c r="D9" t="n">
-        <v>11.7643679720689</v>
+        <v>1.911709795461197</v>
       </c>
       <c r="E9" t="n">
-        <v>7.799163418033405</v>
+        <v>1.267364055430428</v>
       </c>
       <c r="F9" t="n">
-        <v>7.264191559006734</v>
+        <v>1.180431128338594</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.07512850696033</v>
+        <v>6.024708382381054</v>
       </c>
       <c r="D10" t="n">
-        <v>32.92210424041281</v>
+        <v>5.349841939067082</v>
       </c>
       <c r="E10" t="n">
-        <v>7.799163418033405</v>
+        <v>1.267364055430428</v>
       </c>
       <c r="F10" t="n">
-        <v>7.264191559006734</v>
+        <v>1.180431128338594</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>27.02259908795538</v>
+        <v>4.391172351792749</v>
       </c>
       <c r="D11" t="n">
-        <v>17.56673976092232</v>
+        <v>2.854595211149876</v>
       </c>
       <c r="E11" t="n">
-        <v>7.799163418033405</v>
+        <v>1.267364055430428</v>
       </c>
       <c r="F11" t="n">
-        <v>7.264191559006734</v>
+        <v>1.180431128338594</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.0345583543756</v>
+        <v>5.693115732586036</v>
       </c>
       <c r="D12" t="n">
-        <v>23.15485425150876</v>
+        <v>3.762663815870174</v>
       </c>
       <c r="E12" t="n">
-        <v>7.799163418033405</v>
+        <v>1.267364055430428</v>
       </c>
       <c r="F12" t="n">
-        <v>7.264191559006734</v>
+        <v>1.180431128338594</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>19.78166753217299</v>
+        <v>3.214520973978111</v>
       </c>
       <c r="D13" t="n">
-        <v>19.45159831308245</v>
+        <v>3.160884725875897</v>
       </c>
       <c r="E13" t="n">
-        <v>7.799163418033405</v>
+        <v>1.267364055430428</v>
       </c>
       <c r="F13" t="n">
-        <v>7.264191559006734</v>
+        <v>1.180431128338594</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>18.27270992790075</v>
+        <v>2.969315363283872</v>
       </c>
       <c r="D14" t="n">
-        <v>18.6217812349839</v>
+        <v>3.026039450684883</v>
       </c>
       <c r="E14" t="n">
-        <v>7.799163418033405</v>
+        <v>1.267364055430428</v>
       </c>
       <c r="F14" t="n">
-        <v>7.264191559006734</v>
+        <v>1.180431128338594</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
